--- a/DATAmeg/BIDII SCHOOL PERFORMANCE REPORT.xlsx
+++ b/DATAmeg/BIDII SCHOOL PERFORMANCE REPORT.xlsx
@@ -9,18 +9,33 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.0" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.1" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.10" hidden="1">Sheet1!$B$54:$N$54</definedName>
+    <definedName name="_xlchart.11" hidden="1">Sheet1!$B$54:$L$54</definedName>
+    <definedName name="_xlchart.12" hidden="1">Sheet1!$M$1</definedName>
+    <definedName name="_xlchart.13" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.2" hidden="1">Sheet1!$B$54:$L$54</definedName>
+    <definedName name="_xlchart.3" hidden="1">Sheet1!$M$1</definedName>
+    <definedName name="_xlchart.4" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.5" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.6" hidden="1">Sheet1!$A$54</definedName>
+    <definedName name="_xlchart.7" hidden="1">Sheet1!$B$54:$N$54</definedName>
+    <definedName name="_xlchart.8" hidden="1">Sheet1!$M$2:$M$51</definedName>
+    <definedName name="_xlchart.9" hidden="1">Sheet1!$A$54</definedName>
     <definedName name="_xlcn.WorksheetConnection_Sheet1A1N511" hidden="1">Sheet1!$A$1:$N$51</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="61" r:id="rId3"/>
+    <pivotCache cacheId="61" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -83,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
   <si>
     <t>NAME</t>
   </si>
@@ -351,6 +366,48 @@
   <si>
     <t>PASS</t>
   </si>
+  <si>
+    <t>The best performed subject is Kiswahili while the least performed subject is</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>The highest maximum mark scored across the subjects is 98</t>
+  </si>
+  <si>
+    <t>The highest modal mark scored was 78 in subjects 1 and 5,followed by 3,4,6 in that order upto subject 10</t>
+  </si>
+  <si>
+    <t>with the least modal mark</t>
+  </si>
+  <si>
+    <t>The max contributed 27%,mode 23%,mean and median both contributed 20% while the min contributed 10%</t>
+  </si>
+  <si>
+    <t>This indicates the outliers,while there are students performing so well,scoring upto over 900,</t>
+  </si>
+  <si>
+    <t>in the same class there are students scoring below 600.There's need to look into the root cause</t>
+  </si>
+  <si>
+    <t>There is no correllation between mean and mode</t>
+  </si>
+  <si>
+    <t>We are able to compare the mean,mode,max,min and median across the 11 subjects</t>
+  </si>
+  <si>
+    <t>The means across the subjects are not evenly distributed</t>
+  </si>
+  <si>
+    <t>There was a tie between subject 1 and 5 in the highest modal mark scored followed by subject 9,6,…in</t>
+  </si>
+  <si>
+    <t>that order upto subject2</t>
+  </si>
+  <si>
+    <t>Most of the students are doing averagely well with few of them doing below average and very few at the top way above average</t>
+  </si>
 </sst>
 </file>
 
@@ -416,6 +473,8768 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TOTAL</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{EE3A4CC6-C45F-4D6C-95A9-6419BA50265E}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="size">
+        <cx:f dir="row">_xlchart.10</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MODE</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="sunburst" uniqueId="{F77D4393-191D-47B7-BF45-2BD081172DFB}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.9</cx:f>
+              <cx:v>MODE</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels pos="ctr">
+            <cx:visibility seriesName="0" categoryName="1" value="0"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+        </cx:series>
+      </cx:plotAreaRegion>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.8</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TOTAL</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{EE3A4CC6-C45F-4D6C-95A9-6419BA50265E}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MEAN</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$60:$L$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B36F-4F99-97FD-94745A21B310}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="799906559"/>
+        <c:axId val="799891583"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="799906559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="799891583"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="799891583"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="799906559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MAX</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$55:$L$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6579-4CEC-9275-FB6FEE33EAAE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="284175967"/>
+        <c:axId val="284183039"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="284175967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="284183039"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="284183039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="284175967"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="size">
+        <cx:f dir="row">_xlchart.11</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MODE</a:t>
+            </a:r>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="treemap" uniqueId="{D44D78A3-7B3B-4D30-80B7-C8346632DF0A}">
+          <cx:dataLabels pos="inEnd">
+            <cx:visibility seriesName="0" categoryName="1" value="0"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:parentLabelLayout val="overlapping"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MATHS(MEAN,MODE,MAX,MIN,MEDIAN)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3A76-4F65-9B26-2C878CF1A38E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3A76-4F65-9B26-2C878CF1A38E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-3A76-4F65-9B26-2C878CF1A38E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-3A76-4F65-9B26-2C878CF1A38E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-3A76-4F65-9B26-2C878CF1A38E}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$53:$B$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-3A76-4F65-9B26-2C878CF1A38E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.13</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>TOTAL</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{295257D9-C59C-4CAF-80FE-026B79364806}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.12</cx:f>
+              <cx:v>TOTAL</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MEAN VS MODE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$53:$L$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.319999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68.16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$54:$L$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9087-4535-8D3B-C6BC408C4295}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="741211712"/>
+        <c:axId val="741213792"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="741211712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741213792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="741213792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741211712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MEAN,MODE,MAX,MIN,MEDIAN PER SUBJECT</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$53:$L$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.319999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68.16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DCC5-4509-989C-C4803EF3000E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$54:$L$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DCC5-4509-989C-C4803EF3000E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$55:$L$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DCC5-4509-989C-C4803EF3000E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1561706832"/>
+        <c:axId val="1561690608"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$56:$L$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>33</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-DCC5-4509-989C-C4803EF3000E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$57:$L$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>68.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DCC5-4509-989C-C4803EF3000E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1561706832"/>
+        <c:axId val="1561690608"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1561706832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1561690608"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1561690608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1561706832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MEAN</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$53:$L$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>67.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.06</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.319999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.099999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.459999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70.260000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68.16</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70.400000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F95E-4318-AAE7-686790AAEDF8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="250510143"/>
+        <c:axId val="250501823"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="250510143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="250501823"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="250501823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="250510143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="381">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="850" kern="1200"/>
+    <cs:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:bodyPr/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="410">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="bg1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr lIns="38100" tIns="19050" rIns="38100" bIns="19050">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="-60000000" vert="horz"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="-60000000" vert="horz"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:bodyPr rot="0" vert="horz"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="-60000000" vert="horz"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" Requires="cx">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="11" name="Chart 10"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" Requires="cx">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" Requires="cx">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Chart 5"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" Requires="cx">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="10" name="Chart 9"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" Requires="cx">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="11" name="Chart 10"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5835,5 +14654,77 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A16:M88"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="M34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>95</v>
+      </c>
+      <c r="M52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>98</v>
+      </c>
+      <c r="L70" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>100</v>
+      </c>
+      <c r="L87" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>